--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>22840.55</v>
+        <v>22860.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.13</v>
+        <v>22.15</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1032.107998192499</v>
+        <v>1032.056433408578</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.07955120160957674</v>
+        <v>0.07922185601244425</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04518752824220516</v>
+        <v>0.04514672686230248</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>51.82048064383069</v>
+        <v>51.6887424049777</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>73.3491744961795</v>
+        <v>73.3096530245236</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>22.4979275854431</v>
+        <v>22.49389074940967</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23220.29100369147</v>
+        <v>23214.96466031795</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.01662573815829615</v>
+        <v>0.01552554173407095</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25266.00379575237</v>
+        <v>25264.74148984199</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1061906913691821</v>
+        <v>0.1051918735891648</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4296,6 +4296,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>22860.05</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.0792218560124</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -547,8 +547,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>22860.05</v>
+        <v>22794.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>22.15</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1032.056433408578</v>
+        <v>1031.878678134903</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.07922185601244425</v>
+        <v>0.07903631641315512</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04514672686230248</v>
+        <v>0.04526935264825713</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>51.6887424049777</v>
+        <v>51.61452656526205</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>73.3096530245236</v>
+        <v>73.28738827260891</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -717,13 +717,13 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>22.49389074940967</v>
+        <v>22.49161656403553</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23214.96466031795</v>
+        <v>23208.61956921406</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.01552554173407095</v>
+        <v>0.0181809218667055</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25264.74148984199</v>
+        <v>25260.39004074242</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.1051918735891648</v>
+        <v>0.1081937528293346</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4329,6 +4329,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>22794.2</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0790363164132</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>22794.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>22.09</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.1742424242424243</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>1031.878678134903</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.07903631641315512</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>82.57575757575756</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>51.61452656526205</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>73.28738827260891</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>22.49161656403553</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>23208.61956921406</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.0181809218667055</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>25260.39004074242</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.1081937528293346</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,19 +811,19 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.2391295924614276</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1441412966122997</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.1515792551121545</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="30" t="n">
         <v>0.1288829053514899</v>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -821,19 +836,19 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.1935021774008709</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.09763125598095479</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.1365299354764277</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.1266111612178313</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -846,17 +861,17 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.06000000000000005</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.166570878823761</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.1861008326237956</v>
       </c>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="16" t="n">
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,17 +884,17 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.05380821184473106</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.1426937745530534</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1302514261207753</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,21 +907,20 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.0106087366549088</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1763303040153759</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1569069942012558</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1042,16 +1056,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>12364.35</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>35.37</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,16 +1075,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>13226.35</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>31.33</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1080,16 +1094,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>13473.55</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>30.2</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1099,16 +1113,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>13664.25</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>28.82</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1118,16 +1132,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>14555.9</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>27.21</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1137,16 +1151,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>15052.65</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>28.02</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1156,16 +1170,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>15086.9</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>26.92</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1175,16 +1189,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>14648.35</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>24.7</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1194,16 +1208,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>14996.2</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>25.44</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1213,16 +1227,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>14921.45</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>24.77</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1232,16 +1246,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>14307.95</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>22.67</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1251,16 +1265,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>14894.5</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>23.67</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1270,16 +1284,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>14783.35</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>23.15</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1289,16 +1303,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>14119.6</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>21.07</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1308,16 +1322,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>13387.55</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>20.05</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1327,16 +1341,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>14665.65</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>21.47</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1346,16 +1360,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>15325.05</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>22.25</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1365,16 +1379,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>14829.35</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.65</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1384,16 +1398,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>15424</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>22.21</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1403,16 +1417,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>15946.15</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>23.43</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1422,16 +1436,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>15448.85</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>22.85</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1441,16 +1455,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>14935.5</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>21.76</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1460,16 +1474,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>14518.75</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>21.21</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1479,16 +1493,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>14557.85</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>21.14</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1498,16 +1512,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>15219.55</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>21.82</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1517,16 +1531,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>15766.4</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>22.56</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1536,16 +1550,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>16430</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>23.51</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1555,16 +1569,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>17059</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>24.24</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1574,16 +1588,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>16924.3</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>23.07</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1593,16 +1607,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>17292.6</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>23.45</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1612,16 +1626,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>16801.1</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>21.78</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1631,16 +1645,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>17987.95</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>22.68</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1650,16 +1664,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>19429.15</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>24.48</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1669,16 +1683,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>19802.1</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>24.2</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1688,16 +1702,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>20090.05</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>24.37</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1707,16 +1721,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>20255.15</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>24.74</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1726,16 +1740,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>20997.2</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>24.73</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1745,16 +1759,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>21103.3</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>24.48</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1764,16 +1778,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>22559.7</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>26.23</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1783,16 +1797,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>23530.8</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>27.1</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1802,16 +1816,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>23734.55</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>27.19</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1821,16 +1835,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>24245.2</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>27.87</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1840,16 +1854,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>22689.35</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>26.07</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1859,16 +1873,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>22687</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>25.77</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1878,16 +1892,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>22375.4</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>25.56</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1897,16 +1911,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>21580.9</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>24.27</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1916,16 +1930,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>19880.9</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>21.84</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1935,16 +1949,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>21339.55</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>23.54</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1954,16 +1968,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>22030.05</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>24.09</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1973,16 +1987,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>22801.95</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>24.59</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1992,16 +2006,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>23617.2</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>25.34</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2011,16 +2025,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>22914.95</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>24.27</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2030,16 +2044,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>22462.95</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>23.49</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2049,16 +2063,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>22734.1</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>23.8</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2068,16 +2082,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>23710.4</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>24.6</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2087,16 +2101,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>23933.2</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>24.45</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2106,16 +2120,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>23871.55</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>24.45</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2125,16 +2139,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>23079.5</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>23.48</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2144,16 +2158,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>23166.85</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>23.5</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2163,16 +2177,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>20528.05</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>21.24</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2182,16 +2196,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>22683.55</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>23.23</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2201,16 +2215,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>22657</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>22.45</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2220,16 +2234,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>22995.65</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>22.72</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2239,16 +2253,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>23460.7</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>23.09</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2258,16 +2272,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>23450.35</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>22.73</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2369,13 +2383,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>6724.75</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>23.6</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2383,12 +2397,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2396,31 +2410,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>6452.15</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>22.81</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2428,12 +2442,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2441,31 +2455,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>6980.8</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>25.89</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2473,12 +2487,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2486,31 +2500,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>7394.85</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>27.49</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2518,12 +2532,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2531,28 +2545,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>6982.8</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>25.3</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2560,15 +2574,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2576,28 +2590,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>7995.05</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>26.82</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2605,15 +2619,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2621,28 +2635,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>8331.6</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>27.72</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2650,15 +2664,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2666,28 +2680,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>8600</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>29.58</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2695,15 +2709,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2711,28 +2725,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>9490.65</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>32.55</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2740,15 +2754,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2756,28 +2770,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>8912.1</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>29.65</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2785,15 +2799,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2801,28 +2815,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>9162.450000000001</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>30.47</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2830,15 +2844,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2846,28 +2860,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>9116</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>30.21</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2875,15 +2889,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2891,28 +2905,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>9170</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>29.61</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2920,15 +2934,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2936,28 +2950,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>9663.700000000001</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>31.22</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2965,15 +2979,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2981,28 +2995,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>9657.950000000001</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>30.96</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3010,15 +3024,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3026,28 +3040,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>9340.9</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>28.22</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3055,15 +3069,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3071,28 +3085,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>9872.549999999999</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>30.84</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3100,15 +3114,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3116,28 +3130,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>6996.75</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>21.8</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3145,15 +3159,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3161,28 +3175,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>8474.799999999999</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>29.35</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3190,15 +3204,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3206,28 +3220,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>9341.75</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>40.63</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3235,15 +3249,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3251,28 +3265,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>11518.3</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>43.39</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3280,15 +3294,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3296,28 +3310,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>12313.7</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>35.89</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3325,15 +3339,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3341,28 +3355,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>13473.55</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>30.2</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3370,15 +3384,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3386,28 +3400,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>15052.65</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>28.02</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3415,15 +3429,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3431,25 +3445,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>14996.2</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>25.44</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,15 +3471,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3473,25 +3487,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>14894.5</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>23.67</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3499,15 +3513,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3515,25 +3529,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>13387.55</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>20.05</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3541,15 +3555,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3557,25 +3571,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>14829.35</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>21.65</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3583,15 +3597,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3599,25 +3613,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>15448.85</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>22.85</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3625,15 +3639,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3641,25 +3655,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>14557.85</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>21.14</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3667,15 +3681,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3683,25 +3697,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>16430</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>23.51</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3709,15 +3723,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3725,25 +3739,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>17292.6</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>23.45</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3751,15 +3765,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3767,22 +3781,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>19429.15</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>24.48</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3790,15 +3804,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3806,22 +3820,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>20255.15</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>24.74</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3829,15 +3843,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3845,22 +3859,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>22559.7</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>26.23</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3868,15 +3882,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3884,22 +3898,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>24245.2</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>27.87</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3907,15 +3921,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3923,22 +3937,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>22375.4</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>25.56</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3946,15 +3960,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3962,22 +3976,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>21339.55</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>23.54</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3985,15 +3999,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4001,22 +4015,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>23617.2</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>25.34</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4024,15 +4038,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4040,22 +4054,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>22734.1</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>23.8</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4063,15 +4077,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4079,19 +4093,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>23871.55</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>24.45</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4099,15 +4113,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4115,19 +4129,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>20528.05</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>21.24</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4135,15 +4149,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4151,19 +4165,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>22995.65</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>22.72</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4171,15 +4185,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4187,10 +4201,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4267,30 +4281,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>22840.55</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>22.13</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.174242424242</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.0795512016096</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4300,30 +4314,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>22860.05</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>22.15</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.174242424242</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.0792218560124</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4333,30 +4347,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>22794.2</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>22.09</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.174242424242</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.0790363164132</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4476,4 +4490,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty 500 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22794.2</v>
+        <v>22935.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.09</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1742424242424243</v>
+        <v>0.1893939393939394</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1031.878678134903</v>
+        <v>1031.718398560504</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07903631641315512</v>
+        <v>0.06996787006263983</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04526935264825713</v>
+        <v>0.0449842555105713</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>82.57575757575756</v>
+        <v>81.06060606060606</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>51.61452656526205</v>
+        <v>47.98714802505593</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.28738827260891</v>
+        <v>71.13856864994102</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.49161656403553</v>
+        <v>22.32356967568169</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23208.61956921406</v>
+        <v>23031.63755594814</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0181809218667055</v>
+        <v>0.004209162198906435</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.48</v>
+        <v>24.45674973706654</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25260.39004074242</v>
+        <v>25232.47867272131</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1081937528293346</v>
+        <v>0.1001686791302987</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4379,6 +4379,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>22935.1</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.189393939394</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.0699678700626</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22935.1</v>
+        <v>22552.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.23</v>
+        <v>21.85</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1893939393939394</v>
+        <v>0.1742424242424243</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1031.718398560504</v>
+        <v>1032.155606407322</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06996787006263983</v>
+        <v>0.07053037990495525</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0449842555105713</v>
+        <v>0.04576659038901602</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>81.06060606060606</v>
+        <v>82.57575757575756</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>47.98714802505593</v>
+        <v>48.2121519619821</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.13856864994102</v>
+        <v>72.26667589162491</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.32356967568169</v>
+        <v>22.33610560931043</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23031.63755594814</v>
+        <v>23054.33662995581</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.004209162198906435</v>
+        <v>0.02224739630711348</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45674973706654</v>
+        <v>24.45863012711085</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25232.47867272131</v>
+        <v>25245.1122107405</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1001686791302987</v>
+        <v>0.1193881065039288</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4412,6 +4412,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>22552.6</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.070530379905</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4452,7 +4485,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22552.6</v>
+        <v>22603.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.85</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1032.155606407322</v>
+        <v>1032.123287671233</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07053037990495525</v>
+        <v>0.07057057950470136</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04576659038901602</v>
+        <v>0.04566210045662101</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.2121519619821</v>
+        <v>48.22823180188054</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.26667589162491</v>
+        <v>72.27149984359446</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.33610560931043</v>
+        <v>22.33700148610477</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23054.33662995581</v>
+        <v>23054.53941055567</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02224739630711348</v>
+        <v>0.01995440575820884</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45863012711085</v>
+        <v>24.45876450863</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25245.1122107405</v>
+        <v>25244.46043702366</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1193881065039288</v>
+        <v>0.1168385620378996</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4445,6 +4445,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>22603.5</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.174242424242</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.0705705795047</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4485,7 +4518,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22603.5</v>
+        <v>22232.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.9</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1742424242424243</v>
+        <v>0.09848484848484848</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1032.123287671233</v>
+        <v>1032.133240482823</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07057057950470136</v>
+        <v>0.07061588312388634</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04566210045662101</v>
+        <v>0.04642525533890437</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>82.57575757575756</v>
+        <v>90.15151515151516</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.22823180188054</v>
+        <v>48.24635324955453</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.27149984359446</v>
+        <v>77.57996658092696</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.33700148610477</v>
+        <v>22.33801110961804</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23054.53941055567</v>
+        <v>23055.80379251136</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01995440575820884</v>
+        <v>0.03704786952729977</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45876450863</v>
+        <v>24.45891595215699</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25244.46043702366</v>
+        <v>25244.8601803968</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1168385620378996</v>
+        <v>0.1355114183916895</v>
       </c>
     </row>
     <row r="16">
@@ -4222,13 +4222,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -4478,6 +4478,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>22232.15</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.09848484848480001</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.07061588312390001</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4518,7 +4551,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22232.15</v>
+        <v>22101</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.54</v>
+        <v>21.42</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09848484848484848</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1032.133240482823</v>
+        <v>1031.792717086835</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07061588312388634</v>
+        <v>0.07040253115024053</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04642525533890437</v>
+        <v>0.04668534080298786</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.15151515151516</v>
+        <v>91.66666666666666</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.24635324955453</v>
+        <v>48.16101246009621</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.57996658092696</v>
+        <v>78.61497040469553</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.33801110961804</v>
+        <v>22.33325640849107</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23055.80379251136</v>
+        <v>23043.29131111397</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03704786952729977</v>
+        <v>0.04263568667091855</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45891595215699</v>
+        <v>24.45820274698794</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25244.8601803968</v>
+        <v>25235.79546737537</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1355114183916895</v>
+        <v>0.141839530671706</v>
       </c>
     </row>
     <row r="16">
@@ -4222,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4511,6 +4511,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>22101</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.08333333333329999</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.0704025311502</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4551,7 +4584,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4621,17 +4654,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3M India Ltd.</t>
+          <t>Aadhar Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3MINDIA</t>
+          <t>AADHARHFC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4641,17 +4674,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aadhar Housing Finance Ltd.</t>
+          <t>Aarti Industries Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AADHARHFC</t>
+          <t>AARTIIND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -4661,17 +4694,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aarti Industries Ltd.</t>
+          <t>Aavas Financiers Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AARTIIND</t>
+          <t>AAVAS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4681,17 +4714,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aavas Financiers Ltd.</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AAVAS</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4701,17 +4734,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4721,17 +4754,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>ACC Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ACC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -4741,17 +4774,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACC Ltd.</t>
+          <t>ACME Solar Holdings Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>ACMESOLAR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -4761,17 +4794,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACME Solar Holdings Ltd.</t>
+          <t>Action Construction Equipment Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ACMESOLAR</t>
+          <t>ACE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4781,17 +4814,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Action Construction Equipment Ltd.</t>
+          <t>Acutaas Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACE</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -4801,17 +4834,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals Ltd.</t>
+          <t>Adani Energy Solutions Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -4821,17 +4854,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adani Energy Solutions Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -4841,17 +4874,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -4861,17 +4894,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -4881,17 +4914,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Ltd.</t>
+          <t>Adani Power Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -4901,17 +4934,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adani Power Ltd.</t>
+          <t>Adani Total Gas Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -4921,17 +4954,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adani Total Gas Ltd.</t>
+          <t>Aditya Birla Capital Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4941,17 +4974,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Aditya Birla Real Estate Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>ABREL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -4961,17 +4994,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>Aditya Birla Sun Life AMC Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>ABSLAMC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4981,17 +5014,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aditya Birla Lifestyle Brands Ltd.</t>
+          <t>Aditya Infotech Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ABLBL</t>
+          <t>CPPLUS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5001,17 +5034,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aditya Birla Real Estate Ltd.</t>
+          <t>Aegis Logistics Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ABREL</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5021,17 +5054,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aditya Birla Sun Life AMC Ltd.</t>
+          <t>Aegis Vopak Terminals Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ABSLAMC</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -5041,17 +5074,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditya Infotech Ltd.</t>
+          <t>Aether Industries Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CPPLUS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5061,17 +5094,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>Afcons Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>AFCONS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -5081,17 +5114,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aegis Vopak Terminals Ltd.</t>
+          <t>Affle 3i Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>AFFLE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -5101,17 +5134,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure Ltd.</t>
+          <t>AIA Engineering Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AFCONS</t>
+          <t>AIAENG</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5121,17 +5154,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Affle 3i Ltd.</t>
+          <t>Ajanta Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AFFLE</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5141,17 +5174,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AIA Engineering Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AIAENG</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5161,17 +5194,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ajanta Pharmaceuticals Ltd.</t>
+          <t>Allied Blenders and Distillers Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5181,17 +5214,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5201,17 +5234,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Ltd.</t>
+          <t>Amber Enterprises India Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5221,17 +5254,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>Ambuja Cements Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -5241,17 +5274,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Anand Rathi Wealth Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5261,17 +5294,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ambuja Cements Ltd.</t>
+          <t>Anant Raj Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5314,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Angel One Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5301,17 +5334,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Anant Raj Ltd.</t>
+          <t>Anthem Biosciences Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>ANTHEM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5321,17 +5354,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Angel One Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5341,17 +5374,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5394,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5381,17 +5414,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5434,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>APL Apollo Tubes Ltd.</t>
+          <t>Apollo Tyres Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>APOLLOTYRE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5421,17 +5454,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Aptus Value Housing Finance India Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>APTUS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5441,12 +5474,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apollo Tyres Ltd.</t>
+          <t>Asahi India Glass Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>APOLLOTYRE</t>
+          <t>ASAHIINDIA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5461,17 +5494,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aptus Value Housing Finance India Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>APTUS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5481,17 +5514,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Asahi India Glass Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -5501,17 +5534,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>Aster DM Quality Care Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5521,17 +5554,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Astral Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5541,17 +5574,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aster DM Quality Care Ltd.</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ASTERDM</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5561,17 +5594,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astral Ltd.</t>
+          <t>Atul Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ATUL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5581,17 +5614,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5601,17 +5634,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Atul Ltd.</t>
+          <t>Aurobindo Pharma Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ATUL</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5654,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5641,17 +5674,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aurobindo Pharma Ltd.</t>
+          <t>Avanti Feeds Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5661,17 +5694,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Authum Investment &amp; Infrastructure Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AIIL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -5681,17 +5714,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>AWL Agri Business Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>AWL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5701,17 +5734,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5721,17 +5754,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Azad Engineering Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5741,17 +5774,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Bagmane Prime Office REIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>BAGMANE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -5761,17 +5794,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5814,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5801,12 +5834,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5821,12 +5854,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5841,17 +5874,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Balkrishna Industries Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BALKRISIND</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5894,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Balkrishna Industries Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>BALKRISIND</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5881,17 +5914,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bandhan Bank Ltd.</t>
+          <t>Balrampur Chini Mills Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5901,12 +5934,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Bandhan Bank Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5921,12 +5954,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5941,12 +5974,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bank of Maharashtra</t>
+          <t>Bank of India</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5961,17 +5994,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5981,17 +6014,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BAYERCROP</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6061,17 +6094,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Bharat Coking Coal Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>BHARATCOAL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6101,17 +6134,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Bharat Electronics Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6121,17 +6154,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6174,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd.</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6161,17 +6194,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Bharat Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6214,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6201,17 +6234,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bikaji Foods International Ltd.</t>
+          <t>Bharti Hexacom Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BIKAJI</t>
+          <t>BHARTIHEXA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -6281,17 +6314,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BLS International Services Ltd.</t>
+          <t>Black Box Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BLS</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -6301,17 +6334,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Blue Dart Express Ltd.</t>
+          <t>BLS International Services Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BLUEDART</t>
+          <t>BLS</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6321,17 +6354,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -6341,17 +6374,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Blue Star Ltd.</t>
+          <t>Bosch Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6361,17 +6394,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bombay Burmah Trading Corporation Ltd.</t>
+          <t>Brainbees Solutions Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BBTC</t>
+          <t>FIRSTCRY</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6381,17 +6414,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bosch Ltd.</t>
+          <t>Brigade Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>BRIGADE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -6401,17 +6434,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Brainbees Solutions Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6454,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Brigade Enterprises Ltd.</t>
+          <t>Brookfield India Real Estate Trust</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>BIRET</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6441,17 +6474,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Britannia Industries Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6494,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Can Fin Homes Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CANFINHOME</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6481,17 +6514,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>C.E. Info Systems Ltd.</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAPMYINDIA</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6501,12 +6534,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Can Fin Homes Ltd.</t>
+          <t>Canara HSBC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6521,17 +6554,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Caplin Point Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>CAPLIPOINT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6574,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Canara HSBC Life Insurance Company Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6561,17 +6594,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Caplin Point Laboratories Ltd.</t>
+          <t>Carborundum Universal Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>CARBORUNIV</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6581,17 +6614,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capri Global Capital Ltd.</t>
+          <t>Cartrade Tech Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -6601,17 +6634,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CARBORUNIV</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6621,17 +6654,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cartrade Tech Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -6641,17 +6674,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Ceat Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>CEATLTD</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6661,17 +6694,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>Cemindia Projects Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -6681,17 +6714,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ceat Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CEATLTD</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6701,17 +6734,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cemindia Projects Ltd.</t>
+          <t>Central Depository Services (India) Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6721,17 +6754,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Central Mine Planning &amp; Design Institute Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>CMPDI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -6741,17 +6774,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6761,17 +6794,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>CESC Ltd.</t>
+          <t>CG Power and Industrial Solutions Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CESC</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -6781,17 +6814,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CG Power and Industrial Solutions Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6801,17 +6834,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Chalet Hotels Ltd.</t>
+          <t>Chennai Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>CHENNPETRO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -6821,17 +6854,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Choice International Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6841,17 +6874,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CHENNPETRO</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6861,12 +6894,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Choice International Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6881,17 +6914,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>CIE Automotive India Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -6901,17 +6934,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -6921,17 +6954,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CIE Automotive India Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -6941,17 +6974,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>Clean Max Enviro Energy Solutions Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CLEANMAX</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -6961,17 +6994,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -6981,17 +7014,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Coal India Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -7001,17 +7034,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Coal India Ltd.</t>
+          <t>Cochin Shipyard Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7021,17 +7054,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -7041,17 +7074,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Coforge Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7061,17 +7094,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7081,17 +7114,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7101,17 +7134,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Concord Biotech Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>CONCORDBIO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7121,17 +7154,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Concord Biotech Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CONCORDBIO</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7141,17 +7174,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7161,17 +7194,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Craftsman Automation Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>CRAFTSMAN</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7181,17 +7214,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Craftsman Automation Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CRAFTSMAN</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7201,12 +7234,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7221,17 +7254,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CRISIL Ltd.</t>
+          <t>Crompton Greaves Consumer Electricals Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7241,17 +7274,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Crompton Greaves Consumer Electricals Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7261,17 +7294,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Cupid Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7361,17 +7394,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DCM Shriram Ltd.</t>
+          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DCMSHRIRAM</t>
+          <t>DEEPAKFERT</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7414,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deepak Fertilisers &amp; Petrochemicals Corp. Ltd.</t>
+          <t>Deepak Nitrite Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DEEPAKFERT</t>
+          <t>DEEPAKNTR</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7401,17 +7434,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deepak Nitrite Ltd.</t>
+          <t>Delhivery Ltd.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DEEPAKNTR</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7454,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Delhivery Ltd.</t>
+          <t>Devyani International Ltd.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7441,17 +7474,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Devyani International Ltd.</t>
+          <t>Divi's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7461,17 +7494,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Divi's Laboratories Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7514,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>DLF Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7501,17 +7534,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>DOMS Industries Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DOMS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7521,17 +7554,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DOMS Industries Ltd.</t>
+          <t>Dr. Lal Path Labs Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DOMS</t>
+          <t>LALPATHLAB</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -7541,12 +7574,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dr. Lal Path Labs Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LALPATHLAB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7561,17 +7594,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Dummy HEG Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>DUMMYHEG</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -7581,17 +7614,17 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dummy HEG Ltd.</t>
+          <t>E.I.D. Parry (India) Ltd.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DUMMYHEG</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7601,17 +7634,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>E.I.D. Parry (India) Ltd.</t>
+          <t>eClerx Services Ltd.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>EIDPARRY</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7621,17 +7654,17 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7641,17 +7674,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>EIH Ltd.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>EIHOTEL</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7694,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EIH Ltd.</t>
+          <t>Elecon Engineering Co. Ltd.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>EIHOTEL</t>
+          <t>ELECON</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7714,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Elecon Engineering Co. Ltd.</t>
+          <t>Elgi Equipments Ltd.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ELECON</t>
+          <t>ELGIEQUIP</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7701,17 +7734,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Elgi Equipments Ltd.</t>
+          <t>Emami Ltd.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ELGIEQUIP</t>
+          <t>EMAMILTD</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -7721,17 +7754,17 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Emami Ltd.</t>
+          <t>EMBASSY OFFICE PARKS REIT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>EMAMILTD</t>
+          <t>EMBASSY</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -7821,17 +7854,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Ltd.</t>
+          <t>Escorts Kubota Ltd.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>ESCORTS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7841,17 +7874,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Escorts Kubota Ltd.</t>
+          <t>Eternal Ltd.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -7861,17 +7894,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -7881,17 +7914,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7901,17 +7934,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>Fertilisers and Chemicals Travancore Ltd.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -7921,17 +7954,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Fertilisers and Chemicals Travancore Ltd.</t>
+          <t>Finolex Cables Ltd.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FACT</t>
+          <t>FINCABLES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -7941,17 +7974,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Finolex Cables Ltd.</t>
+          <t>Firstsource Solutions Ltd.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>FSL</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -7961,17 +7994,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Firstsource Solutions Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -7981,17 +8014,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Force Motors Ltd.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8001,17 +8034,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Force Motors Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8021,17 +8054,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Fractal Analytics Ltd.</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -8301,17 +8334,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Go Digit General Insurance Ltd.</t>
+          <t>Godawari Power &amp; Ispat Ltd.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>GODIGIT</t>
+          <t>GPIL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8321,17 +8354,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Godfrey Phillips India Ltd.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8341,12 +8374,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Godfrey Phillips India Ltd.</t>
+          <t>Godrej Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8361,17 +8394,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Godrej Consumer Products Ltd.</t>
+          <t>Godrej Industries Ltd.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>GODREJIND</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Diversified</t>
         </is>
       </c>
     </row>
@@ -8381,17 +8414,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Godrej Industries Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>GODREJIND</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -8401,17 +8434,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Granules India Ltd.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -8421,17 +8454,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8441,17 +8474,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Graphite India Ltd.</t>
+          <t>Grasim Industries Ltd.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -8461,17 +8494,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Grasim Industries Ltd.</t>
+          <t>Gravita India Ltd.</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8481,17 +8514,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Gravita India Ltd.</t>
+          <t>Great Eastern Shipping Co. Ltd.</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -8501,17 +8534,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Great Eastern Shipping Co. Ltd.</t>
+          <t>Gujarat Fluorochemicals Ltd.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>FLUOROCHEM</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8521,17 +8554,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Gujarat Fluorochemicals Ltd.</t>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FLUOROCHEM</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8541,17 +8574,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Gujarat Mineral Development Corporation Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -8561,17 +8594,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Havells India Ltd.</t>
+          <t>HBL Engineering Ltd.</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>HBLENGINE</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8581,17 +8614,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HBL Engineering Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>HBLENGINE</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -8601,17 +8634,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>HCL Technologies Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8621,12 +8654,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -8641,12 +8674,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>HDFC Bank Ltd.</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -8661,12 +8694,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -8681,17 +8714,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>HEG Advanced Materials Ltd.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HEGAM</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8734,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HEG Advanced Materials Ltd.</t>
+          <t>Hero MotoCorp Ltd.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HEGAM</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -8721,17 +8754,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -8741,17 +8774,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Hexaware Technologies Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HEXT</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -8761,17 +8794,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>HFCL Ltd.</t>
+          <t>Himadri Speciality Chemical Ltd.</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>HSCL</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -8781,17 +8814,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8801,17 +8834,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>Hindustan Aeronautics Ltd.</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8821,17 +8854,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8841,17 +8874,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Hindustan Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -8861,17 +8894,17 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Hindustan Petroleum Corporation Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8881,17 +8914,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Hindustan Zinc Ltd.</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -8901,17 +8934,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Ltd.</t>
+          <t>Hitachi Energy India Ltd.</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8921,17 +8954,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Ltd.</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -8941,17 +8974,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Honasa Consumer Ltd.</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>HONASA</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -8961,17 +8994,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Honasa Consumer Ltd.</t>
+          <t>Honeywell Automation India Ltd.</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -8981,17 +9014,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>Housing &amp; Urban Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>HUDCO</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9001,17 +9034,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Housing &amp; Urban Development Corporation Ltd.</t>
+          <t>Hyundai Motor India Ltd.</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>HUDCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9021,17 +9054,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9074,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9061,12 +9094,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9081,12 +9114,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9101,12 +9134,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9121,12 +9154,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9141,12 +9174,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>IFCI Ltd.</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>IFCI</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9161,12 +9194,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IFCI Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>IFCI</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9181,17 +9214,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>IIFL Finance Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -9201,17 +9234,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Indegene Ltd.</t>
+          <t>Indiamart Intermesh Ltd.</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>INDGN</t>
+          <t>INDIAMART</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9221,17 +9254,17 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9241,17 +9274,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Indiamart Intermesh Ltd.</t>
+          <t>Indian Energy Exchange Ltd.</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>INDIAMART</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9261,17 +9294,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9281,17 +9314,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Indian Energy Exchange Ltd.</t>
+          <t>Indian Oil Corporation Ltd.</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -9301,17 +9334,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Indian Hotels Co. Ltd.</t>
+          <t>Indian Overseas Bank</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>IOB</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9321,17 +9354,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Indian Oil Corporation Ltd.</t>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9341,12 +9374,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Indian Overseas Bank</t>
+          <t>Indian Railway Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>IOB</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -9361,17 +9394,17 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>Indian Renewable Energy Development Agency Ltd.</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9381,17 +9414,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Indian Railway Finance Corporation Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -9401,17 +9434,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Indian Renewable Energy Development Agency Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -9421,17 +9454,17 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9441,17 +9474,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Info Edge (India) Ltd.</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9461,17 +9494,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Infosys Ltd.</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9481,17 +9514,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>INOX India Ltd.</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9501,17 +9534,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>Inox Wind Ltd.</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9521,17 +9554,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Inox Wind Ltd.</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9541,17 +9574,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -9561,12 +9594,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>International Gemological Institute Ltd.</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>IGIL</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -9581,17 +9614,17 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Inventurus Knowledge Solutions Ltd.</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -9601,17 +9634,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Inventurus Knowledge Solutions Ltd.</t>
+          <t>Ipca Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IKS</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -9621,17 +9654,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Ipca Laboratories Ltd.</t>
+          <t>IRB Infrastructure Developers Ltd.</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -9641,12 +9674,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>IRB Infrastructure Developers Ltd.</t>
+          <t>IRCON International Ltd.</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>IRB</t>
+          <t>IRCON</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -9661,17 +9694,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IRCON International Ltd.</t>
+          <t>ITC Hotels Ltd.</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IRCON</t>
+          <t>ITCHOTELS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -9681,17 +9714,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ITC Hotels Ltd.</t>
+          <t>ITC Ltd.</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -9701,17 +9734,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ITC Ltd.</t>
+          <t>ITI Ltd.</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ITI</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -9721,17 +9754,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>ITI Ltd.</t>
+          <t>J.K. Cement Ltd.</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>JKCEMENT</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -9741,17 +9774,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>J.K. Cement Ltd.</t>
+          <t>Jain Resource Recycling Ltd.</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>JKCEMENT</t>
+          <t>JAINREC</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -9761,17 +9794,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jain Resource Recycling Ltd.</t>
+          <t>Jaiprakash Power Ventures Ltd.</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>JAINREC</t>
+          <t>JPPOWER</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -9781,17 +9814,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Jaiprakash Power Ventures Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>JPPOWER</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9801,17 +9834,17 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>JBM Auto Ltd.</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>JBMA</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9821,17 +9854,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>JBM Auto Ltd.</t>
+          <t>Jindal Saw Ltd.</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>JBMA</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -9841,17 +9874,17 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Jindal Saw Ltd.</t>
+          <t>Jindal Stainless Ltd.</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -9861,12 +9894,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Jindal Stainless Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -9881,17 +9914,17 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Jio Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9901,17 +9934,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jio Financial Services Ltd.</t>
+          <t>JK Tyre &amp; Industries Ltd.</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>JKTYRE</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -9921,17 +9954,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>JK Tyre &amp; Industries Ltd.</t>
+          <t>JM Financial Ltd.</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>JKTYRE</t>
+          <t>JMFINANCIL</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -9941,17 +9974,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>JM Financial Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>JMFINANCIL</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -9961,17 +9994,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -9981,17 +10014,17 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>JSW Dulux Ltd.</t>
+          <t>JSW Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>JSWINFRA</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10001,17 +10034,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>JSW Steel Ltd.</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -10021,17 +10054,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>JSW Infrastructure Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>JSWINFRA</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10041,17 +10074,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>JSW Steel Ltd.</t>
+          <t>Jubilant Ingrevia Ltd.</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10061,17 +10094,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>Jupiter Wagons Ltd.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>JWL</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10081,17 +10114,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Jubilant Ingrevia Ltd.</t>
+          <t>Jyoti CNC Automation Ltd.</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>JYOTICNC</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10101,17 +10134,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>JUBLPHARMA</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -10121,17 +10154,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Jupiter Wagons Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>JWL</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10141,17 +10174,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd.</t>
+          <t>Kalpataru Projects International Ltd.</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>JYOTICNC</t>
+          <t>KPIL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -10161,17 +10194,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>Kalyan Jewellers India Ltd.</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10181,17 +10214,17 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10201,17 +10234,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Kalpataru Projects International Ltd.</t>
+          <t>Kaynes Technology India Ltd.</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>KPIL</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10221,17 +10254,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Kalyan Jewellers India Ltd.</t>
+          <t>Kec International Ltd.</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>KEC</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -10241,17 +10274,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10261,17 +10294,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Kaynes Technology India Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10281,17 +10314,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Kec International Ltd.</t>
+          <t>Kirloskar Brothers Ltd.</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10301,12 +10334,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>KEI Industries Ltd.</t>
+          <t>Kirloskar Oil Eng Ltd.</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -10321,12 +10354,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Kfin Technologies Ltd.</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -10341,17 +10374,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Eng Ltd.</t>
+          <t>KPIT Technologies Ltd.</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -10361,17 +10394,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>Krishna Institute of Medical Sciences Ltd.</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>KIMS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10381,17 +10414,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>KPIT Technologies Ltd.</t>
+          <t>KSB Ltd.</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10401,17 +10434,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Krishna Institute of Medical Sciences Ltd.</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10421,17 +10454,17 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -10441,17 +10474,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -10461,17 +10494,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10481,17 +10514,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Latent View Analytics Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10501,17 +10534,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>Lenskart Solutions Ltd.</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10521,17 +10554,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Leela Palaces Hotels &amp; Resorts Ltd.</t>
+          <t>LG Electronics India Ltd.</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>LGEINDIA</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -10541,17 +10574,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>LIC Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10561,17 +10594,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Lenskart Solutions Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10581,17 +10614,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>LG Electronics India Ltd.</t>
+          <t>Linde India Ltd.</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>LGEINDIA</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -10601,17 +10634,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -10621,17 +10654,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Lodha Developers Ltd.</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -10641,17 +10674,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -10661,17 +10694,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Lloyds Metals And Energy Ltd.</t>
+          <t>LTM Ltd.</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>LLOYDSME</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -10681,17 +10714,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Lodha Developers Ltd.</t>
+          <t>Lupin Ltd.</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10701,17 +10734,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>Mahanagar Gas Ltd.</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -10721,17 +10754,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>LTM Ltd.</t>
+          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>M&amp;MFIN</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10741,17 +10774,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Lupin Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10761,17 +10794,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Ltd.</t>
+          <t>Manappuram Finance Ltd.</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10781,17 +10814,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>MRPL</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -10801,17 +10834,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Mankind Pharma Ltd.</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10821,17 +10854,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd.</t>
+          <t>Marico Ltd.</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -10841,17 +10874,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Mangalore Refinery &amp; Petrochemicals Ltd.</t>
+          <t>Maruti Suzuki India Ltd.</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>MRPL</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10861,17 +10894,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -10881,17 +10914,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -10901,17 +10934,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Maruti Suzuki India Ltd.</t>
+          <t>Mazagoan Dock Shipbuilders Ltd.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -10921,17 +10954,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>Meesho Ltd.</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -10941,17 +10974,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -10961,17 +10994,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Mazagoan Dock Shipbuilders Ltd.</t>
+          <t>MMTC Ltd.</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>MMTC</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -10981,17 +11014,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Meesho Ltd.</t>
+          <t>Motherson Sumi Wiring India Ltd.</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11001,17 +11034,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Minda Corporation Ltd.</t>
+          <t>Motilal Oswal Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11021,17 +11054,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MMTC Ltd.</t>
+          <t>MphasiS Ltd.</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>MMTC</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11041,12 +11074,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Motherson Sumi Wiring India Ltd.</t>
+          <t>MRF Ltd.</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>MRF</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -11061,17 +11094,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Ltd.</t>
+          <t>MTAR Technologies Ltd.</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -11081,17 +11114,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>MphasiS Ltd.</t>
+          <t>Multi Commodity Exchange of India Ltd.</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11101,17 +11134,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>MRF Ltd.</t>
+          <t>Muthoot Finance Ltd.</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>MRF</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11121,17 +11154,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Ltd.</t>
+          <t>Narayana Hrudayalaya Ltd.</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11141,17 +11174,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Muthoot Finance Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11161,17 +11194,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Narayana Hrudayalaya Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -11181,17 +11214,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>NATCO Pharma Ltd.</t>
+          <t>Nava Ltd.</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>NATCOPHARM</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -11201,17 +11234,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11221,17 +11254,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Nava Ltd.</t>
+          <t>NBCC (India) Ltd.</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11241,17 +11274,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>NCC Ltd.</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>NCC</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -11261,17 +11294,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>NBCC (India) Ltd.</t>
+          <t>Nestle India Ltd.</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11281,17 +11314,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>NCC Ltd.</t>
+          <t>Netweb Technologies India Ltd.</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>NCC</t>
+          <t>NETWEB</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11301,17 +11334,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Nestle India Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11321,17 +11354,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -11341,17 +11374,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Nippon Life India Asset Management Ltd.</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11361,17 +11394,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Newgen Software Technologies Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>NEWGEN</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -11381,17 +11414,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>NHPC Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -11401,17 +11434,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Nippon Life India Asset Management Ltd.</t>
+          <t>NMDC Steel Ltd.</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>NSLNISP</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -11421,17 +11454,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Niva Bupa Health Insurance Company Ltd.</t>
+          <t>NTPC Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>NIVABUPA</t>
+          <t>NTPCGREEN</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11474,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -11461,17 +11494,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>Nuvama Wealth Management Ltd.</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11481,17 +11514,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>NMDC Steel Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>NSLNISP</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -11501,17 +11534,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>NTPC Green Energy Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>NTPCGREEN</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -11521,17 +11554,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11541,17 +11574,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Nuvama Wealth Management Ltd.</t>
+          <t>Oil India Ltd.</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11561,17 +11594,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Nuvoco Vistas Corporation Ltd.</t>
+          <t>Ola Electric Mobility Ltd.</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>NUVOCO</t>
+          <t>OLAELEC</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11581,17 +11614,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>Olectra Greentech Ltd.</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>OLECTRA</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -11601,17 +11634,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Oil &amp; Natural Gas Corporation Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11621,17 +11654,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Oil India Ltd.</t>
+          <t>ONE WAM Ltd.</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11641,17 +11674,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Ltd.</t>
+          <t>Onesource Specialty Pharma Ltd.</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>OLAELEC</t>
+          <t>ONESOURCE</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11661,17 +11694,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>OLECTRA</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11681,17 +11714,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>Page Industries Ltd.</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11734,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>ONE WAM Ltd.</t>
+          <t>Paradeep Phosphates Ltd.</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11721,17 +11754,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Onesource Specialty Pharma Ltd.</t>
+          <t>Patanjali Foods Ltd.</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -11741,17 +11774,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11761,17 +11794,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Page Industries Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11781,17 +11814,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Paradeep Phosphates Ltd.</t>
+          <t>Persistent Systems Ltd.</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11834,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Patanjali Foods Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11854,17 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PB Fintech Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -11841,17 +11874,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -11861,17 +11894,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>Physicswallah Ltd.</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -11881,17 +11914,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>PI Industries Ltd.</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11901,17 +11934,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Pfizer Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>PFIZER</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -11921,17 +11954,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>Pine Labs Ltd.</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>PINELABS</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11941,17 +11974,17 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Piramal Finance Ltd.</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>PIRAMALFIN</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -11961,17 +11994,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Physicswallah Ltd.</t>
+          <t>Piramal Pharma Ltd.</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>PPLPHARMA</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -11981,17 +12014,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PI Industries Ltd.</t>
+          <t>PNB Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12001,17 +12034,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12054,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Pine Labs Ltd.</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>PINELABS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12041,12 +12074,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Piramal Finance Ltd.</t>
+          <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>PIRAMALFIN</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -12061,17 +12094,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>Power Finance Corporation Ltd.</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12081,17 +12114,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PNB Housing Finance Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -12101,17 +12134,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Poly Medicure Ltd.</t>
+          <t>Premier Energies Ltd.</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>POLYMED</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12154,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Prestige Estates Projects Ltd.</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -12141,17 +12174,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Prime Focus Ltd.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -12161,17 +12194,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>Privi Speciality Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12181,17 +12214,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>PTC Industries Ltd.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12201,17 +12234,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Premier Energies Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12221,17 +12254,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Prestige Estates Projects Ltd.</t>
+          <t>PVR INOX Ltd.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -12241,17 +12274,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Prime Focus Ltd.</t>
+          <t>R R Kabel Ltd.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>RRKABEL</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12261,17 +12294,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PTC Industries Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -12281,17 +12314,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Rail Vikas Nigam Ltd.</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12301,17 +12334,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Railtel Corporation Of India Ltd.</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>RAILTEL</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -12321,17 +12354,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>R R Kabel Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>RRKABEL</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12341,17 +12374,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Ramkrishna Forgings Ltd.</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12361,17 +12394,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Rail Vikas Nigam Ltd.</t>
+          <t>RBL Bank Ltd.</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12381,17 +12414,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Railtel Corporation Of India Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>RAILTEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12401,17 +12434,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12421,17 +12454,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -12441,17 +12474,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>Reliance Power Ltd.</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>RPOWER</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -12461,17 +12494,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>RHI MAGNESITA INDIA LTD.</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>RHIM</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12481,17 +12514,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Redington Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -12501,17 +12534,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Rubicon Research Ltd.</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12554,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Reliance Power Ltd.</t>
+          <t>Sagility Ltd.</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>RPOWER</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -12541,17 +12574,17 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>RHI MAGNESITA INDIA LTD.</t>
+          <t>Sai Life Sciences Ltd.</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>SAILIFE</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -12561,17 +12594,17 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12581,17 +12614,17 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Sagility Ltd.</t>
+          <t>Samvardhana Motherson International Ltd.</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12601,17 +12634,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Sai Life Sciences Ltd.</t>
+          <t>Sansera Engineering Ltd.</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SAILIFE</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12621,17 +12654,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Sarda Energy and Minerals Ltd.</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -12641,17 +12674,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd.</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12661,17 +12694,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Sapphire Foods India Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SAPPHIRE</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -12681,17 +12714,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Sarda Energy and Minerals Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12701,17 +12734,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Schneider Electric Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>SCHNEIDER</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12721,17 +12754,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>SBFC Finance Ltd.</t>
+          <t>Shipping Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Services</t>
         </is>
       </c>
     </row>
@@ -12741,17 +12774,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Shree Cement Ltd.</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12794,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -12781,17 +12814,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>Shyam Metalics and Energy Ltd.</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12801,12 +12834,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Schneider Electric Infrastructure Ltd.</t>
+          <t>Siemens Energy India Ltd.</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -12821,17 +12854,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Shipping Corporation of India Ltd.</t>
+          <t>Siemens Ltd.</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -12841,17 +12874,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Shree Cement Ltd.</t>
+          <t>Signatureglobal (India) Ltd.</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>SIGNATURE</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -12861,17 +12894,17 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>SJVN Ltd.</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SJVN</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -12881,17 +12914,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Shyam Metalics and Energy Ltd.</t>
+          <t>Sobha Ltd.</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SHYAMMETL</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Realty</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12934,17 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Siemens Energy India Ltd.</t>
+          <t>Solar Industries India Ltd.</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12921,17 +12954,17 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Siemens Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12941,17 +12974,17 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Signatureglobal (India) Ltd.</t>
+          <t>SPR Auto Technologies Ltd.</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -12961,17 +12994,17 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SJVN Ltd.</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SJVN</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -12981,17 +13014,17 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Sobha Ltd.</t>
+          <t>Star Health and Allied Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SOBHA</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13001,17 +13034,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Solar Industries India Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13021,17 +13054,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Sona BLW Precision Forgings Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -13041,17 +13074,17 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Sonata Software Ltd.</t>
+          <t>Sterlite Technologies Ltd.</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SONATSOFTW</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13094,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Sumitomo Chemical India Ltd.</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SUMICHEM</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -13081,17 +13114,17 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Star Health and Allied Insurance Company Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13101,17 +13134,17 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Media Entertainment &amp; Publication</t>
         </is>
       </c>
     </row>
@@ -13121,17 +13154,17 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>Sundaram Finance Ltd.</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13141,17 +13174,17 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Sumitomo Chemical India Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SUMICHEM</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13161,17 +13194,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Suzlon Energy Ltd.</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13181,17 +13214,17 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>Swan Corp Ltd.</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>SWANCORP</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Media Entertainment &amp; Publication</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -13201,17 +13234,17 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>Swiggy Ltd.</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13221,17 +13254,17 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13241,17 +13274,17 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Supreme Petrochem Ltd.</t>
+          <t>Syrma SGS Technology Ltd.</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13261,17 +13294,17 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Suzlon Energy Ltd.</t>
+          <t>Tata Capital Ltd.</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13281,12 +13314,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Swan Corp Ltd.</t>
+          <t>Tata Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SWANCORP</t>
+          <t>TATACHEM</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -13301,17 +13334,17 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Swiggy Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13354,17 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>Tata Consultancy Services Ltd.</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13341,17 +13374,17 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -13361,17 +13394,17 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Tata Capital Ltd.</t>
+          <t>Tata Elxsi Ltd.</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13381,17 +13414,17 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Tata Chemicals Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>TATACHEM</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13401,17 +13434,17 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Tata Communications Ltd.</t>
+          <t>Tata Motors Ltd.</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>TMCV</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13421,17 +13454,17 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13441,17 +13474,17 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -13461,17 +13494,17 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Tata Elxsi Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -13481,17 +13514,17 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Tata Technologies Ltd.</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>TATATECH</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13501,17 +13534,17 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd.</t>
+          <t>Tata Teleservices (Maharashtra) Ltd.</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>TMCV</t>
+          <t>TTML</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -13521,17 +13554,17 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Ltd.</t>
+          <t>TBO Tek Ltd.</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13541,17 +13574,17 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Tata Power Co. Ltd.</t>
+          <t>TD Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13561,17 +13594,17 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Tech Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Information Technology</t>
         </is>
       </c>
     </row>
@@ -13581,17 +13614,17 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Tata Technologies Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>TATATECH</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Construction</t>
         </is>
       </c>
     </row>
@@ -13601,17 +13634,17 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Tata Teleservices (Maharashtra) Ltd.</t>
+          <t>Tega Industries Ltd.</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>TTML</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13621,17 +13654,17 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>TBO Tek Ltd.</t>
+          <t>Tejas Networks Ltd.</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>TBOTEK</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -13641,17 +13674,17 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>Tenneco Clean Air India Ltd.</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TENNIND</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13661,17 +13694,17 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Thangamayil Jewellery Ltd.</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13681,17 +13714,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Tega Industries Ltd.</t>
+          <t>The New India Assurance Company Ltd.</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>NIACL</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13701,17 +13734,17 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Tejas Networks Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>TEJASNET</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -13721,17 +13754,17 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Tenneco Clean Air India Ltd.</t>
+          <t>Thermax Ltd.</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>TENNIND</t>
+          <t>THERMAX</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13741,17 +13774,17 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Timken India Ltd.</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>TIMKEN</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13761,17 +13794,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Titagarh Rail Systems Ltd.</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13781,17 +13814,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Thermax Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>THERMAX</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Consumer Durables</t>
         </is>
       </c>
     </row>
@@ -13801,17 +13834,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Timken India Ltd.</t>
+          <t>Torrent Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>TIMKEN</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -13821,17 +13854,17 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Titagarh Rail Systems Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -13841,17 +13874,17 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Transformers And Rectifiers (India) Ltd.</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TARIL</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -13861,17 +13894,17 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Torrent Pharmaceuticals Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -13881,17 +13914,17 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Trident Ltd.</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -13901,12 +13934,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Transformers And Rectifiers (India) Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>TARIL</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -13921,17 +13954,17 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Travel Food Services Ltd.</t>
+          <t>Tube Investments of India Ltd.</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>TRAVELFOOD</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13941,17 +13974,17 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>TVS Motor Company Ltd.</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -13961,17 +13994,17 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>UCO Bank</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>UCOBANK</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -13981,17 +14014,17 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Triveni Turbine Ltd.</t>
+          <t>UltraTech Cement Ltd.</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Construction Materials</t>
         </is>
       </c>
     </row>
@@ -14001,17 +14034,17 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Tube Investments of India Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -14021,17 +14054,17 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>TVS Motor Company Ltd.</t>
+          <t>United Breweries Ltd.</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14041,17 +14074,17 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>UCO Bank</t>
+          <t>United Spirits Ltd.</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>UCOBANK</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14061,17 +14094,17 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>UNO Minda Ltd.</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14114,17 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -14101,17 +14134,17 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>United Breweries Ltd.</t>
+          <t>Urban Company Ltd.</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>URBANCO</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -14121,17 +14154,17 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>United Spirits Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -14141,17 +14174,17 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>UNO Minda Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -14161,17 +14194,17 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Vardhman Textiles Ltd.</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>VTL</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Textiles</t>
         </is>
       </c>
     </row>
@@ -14181,17 +14214,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Urban Company Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>URBANCO</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -14201,17 +14234,17 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>Vedanta Aluminium Metal Ltd.</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>VAML</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -14221,17 +14254,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>Vedanta Iron and Steel Ltd.</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>VISL</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -14241,17 +14274,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Vardhman Textiles Ltd.</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>VTL</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -14261,17 +14294,17 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Vedanta Oil and Gas Ltd.</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>VOGL</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Oil Gas &amp; Consumable Fuels</t>
         </is>
       </c>
     </row>
@@ -14281,17 +14314,17 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Vedanta Power Ltd.</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>VEDPOWER</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Power</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22101</v>
+        <v>22072.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.42</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1031.792717086835</v>
+        <v>1013.876894809371</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07040253115024053</v>
+        <v>0.06141303576842816</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04668534080298786</v>
+        <v>0.04593477262287552</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.66666666666666</v>
+        <v>86.56716417910448</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.16101246009621</v>
+        <v>44.56521430737126</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.61497040469553</v>
+        <v>73.96657921758451</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.33325640849107</v>
+        <v>22.06406800022574</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23043.29131111397</v>
+        <v>22370.24875093167</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04263568667091855</v>
+        <v>0.01350794672603306</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45820274698794</v>
+        <v>24.44130427804109</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25235.79546737537</v>
+        <v>24780.47368651129</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.141839530671706</v>
+        <v>0.1227057546183321</v>
       </c>
     </row>
     <row r="16">
@@ -837,22 +837,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
         <v>0.1935021774008709</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.09763125598095479</v>
+        <v>0.08474532333213247</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.1365299354764277</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>0.1266111612178313</v>
+        <v>0.1210836476657601</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="20">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.06000000000000005</v>
+        <v>9.09976554721581e-05</v>
       </c>
       <c r="D20" s="30" t="n">
         <v>0.166570878823761</v>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.05380821184473106</v>
+        <v>0.05407942198866023</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.1426937745530534</v>
@@ -917,7 +917,7 @@
         <v>0.1763303040153759</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1569069942012558</v>
+        <v>0.1348735006127858</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -971,7 +971,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2290,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>22072.1</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2306,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2406,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2451,7 +2470,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2496,7 +2515,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2541,7 +2560,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2560,7 +2579,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2586,7 +2608,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2631,7 +2653,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2676,7 +2698,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2721,7 +2743,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2766,7 +2788,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2811,7 +2833,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2856,7 +2878,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2901,7 +2923,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2946,7 +2968,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2991,7 +3013,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3036,7 +3058,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3081,7 +3103,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3126,7 +3148,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3171,7 +3193,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3216,7 +3238,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3261,7 +3283,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3306,7 +3328,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3351,7 +3373,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3396,7 +3418,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3441,7 +3463,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3456,7 +3478,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3483,7 +3508,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3525,7 +3550,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3567,7 +3592,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3609,7 +3634,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3651,7 +3676,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3693,7 +3718,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3735,7 +3760,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3777,7 +3802,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3788,7 +3813,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3816,7 +3844,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3855,7 +3883,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3894,7 +3922,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3933,7 +3961,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3972,7 +4000,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4011,7 +4039,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4050,7 +4078,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4089,14 +4117,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4125,7 +4156,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4161,7 +4192,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4197,7 +4228,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4208,6 +4239,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>22072.1</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4222,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4230,7 +4297,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4544,6 +4611,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>22072.1</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.134328358209</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.0614130357684</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4584,7 +4684,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22072.1</v>
+        <v>21857.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.77</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1013.876894809371</v>
+        <v>1013.810296846011</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06141303576842816</v>
+        <v>0.06119717224147747</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04593477262287552</v>
+        <v>0.0463821892393321</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>86.56716417910448</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.56521430737126</v>
+        <v>44.47886889659099</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.96657921758451</v>
+        <v>76.55261589285789</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.06406800022574</v>
+        <v>22.05503133623465</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22370.24875093167</v>
+        <v>22359.61786593613</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01350794672603306</v>
+        <v>0.0229606371166351</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44130427804109</v>
+        <v>24.43935040474572</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24780.47368651129</v>
+        <v>24776.86508855894</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1227057546183321</v>
+        <v>0.1335505753592634</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4644,6 +4644,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>21857.75</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.0611971722415</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4684,7 +4717,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7704,7 +7737,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21857.75</v>
+        <v>21971.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.56</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1013.810296846011</v>
+        <v>1013.917858790955</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06119717224147747</v>
+        <v>0.06157191449645105</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0463821892393321</v>
+        <v>0.04614674665436087</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>88.80597014925374</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.47886889659099</v>
+        <v>44.62876579858042</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.55261589285789</v>
+        <v>75.55280884405174</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.05503133623465</v>
+        <v>22.07071911772</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22359.61786593613</v>
+        <v>22377.89626981526</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.0229606371166351</v>
+        <v>0.01849188360498388</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.43935040474572</v>
+        <v>24.44274235749931</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24776.86508855894</v>
+        <v>24782.93299409468</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1335505753592634</v>
+        <v>0.1279530391093355</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4677,6 +4677,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>21971.6</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.111940298507</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.0615719144965</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4717,7 +4750,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21971.6</v>
+        <v>22202.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.67</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1119402985074627</v>
+        <v>0.1865671641791045</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1013.917858790955</v>
+        <v>1013.828767123288</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06157191449645105</v>
+        <v>0.06153894816757943</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04614674665436087</v>
+        <v>0.04566210045662101</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.80597014925374</v>
+        <v>81.34328358208955</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.62876579858042</v>
+        <v>44.61557926703177</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.55280884405174</v>
+        <v>70.32497228757222</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.07071911772</v>
+        <v>22.09214893630059</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22377.89626981526</v>
+        <v>22397.65611919367</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01849188360498388</v>
+        <v>0.008773924031990399</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44274235749931</v>
+        <v>24.44244396512826</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24782.93299409468</v>
+        <v>24780.45283064603</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1279530391093355</v>
+        <v>0.1160933317410164</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4710,6 +4710,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>22202.85</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.186567164179</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.0615389481676</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4750,7 +4783,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22202.85</v>
+        <v>22059.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.9</v>
+        <v>21.75</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1865671641791045</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1013.828767123288</v>
+        <v>1014.248275862069</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06153894816757943</v>
+        <v>0.06190280288021177</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04566210045662101</v>
+        <v>0.04597701149425287</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>81.34328358208955</v>
+        <v>88.80597014925374</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.61557926703177</v>
+        <v>44.7611211520847</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>70.32497228757222</v>
+        <v>75.59251545010302</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.09214893630059</v>
+        <v>22.08457105085961</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22397.65611919367</v>
+        <v>22399.23811148772</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.008773924031990399</v>
+        <v>0.01538257705101653</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44244396512826</v>
+        <v>24.44573737007003</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24780.45283064603</v>
+        <v>24794.04697977048</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1160933317410164</v>
+        <v>0.1239419480491968</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4743,6 +4743,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>22059.9</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.111940298507</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.0619028028802</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4783,7 +4816,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22059.9</v>
+        <v>21616.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.75</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1119402985074627</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1014.248275862069</v>
+        <v>1013.890712945591</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06190280288021177</v>
+        <v>0.06130273444098822</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04597701149425287</v>
+        <v>0.04690431519699812</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.80597014925374</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.7611211520847</v>
+        <v>44.52109377639528</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.59251545010302</v>
+        <v>77.61005947620217</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.08457105085961</v>
+        <v>22.05945047151246</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22399.23811148772</v>
+        <v>22365.87196574972</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01538257705101653</v>
+        <v>0.03468341798838925</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44573737007003</v>
+        <v>24.44030589345443</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24794.04697977048</v>
+        <v>24779.79916692284</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1239419480491968</v>
+        <v>0.1463558111376375</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4776,6 +4776,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>21616.15</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.061302734441</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4816,7 +4849,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21616.15</v>
+        <v>21866.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.32</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1013.890712945591</v>
+        <v>1014.223098330241</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06130273444098822</v>
+        <v>0.06171213365494288</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04690431519699812</v>
+        <v>0.0463821892393321</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.52109377639528</v>
+        <v>44.68485346197715</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.61005947620217</v>
+        <v>76.61441126247374</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.05945047151246</v>
+        <v>22.07658909232063</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22365.87196574972</v>
+        <v>22390.58658977705</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03468341798838925</v>
+        <v>0.02396053303899071</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44030589345443</v>
+        <v>24.44401154119674</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24779.79916692284</v>
+        <v>24791.68112093274</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1463558111376375</v>
+        <v>0.1337667690722051</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4809,6 +4809,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>21866.65</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.0617121336549</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4849,7 +4882,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21866.65</v>
+        <v>21822.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.56</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1014.223098330241</v>
+        <v>1014.539748953975</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06171213365494288</v>
+        <v>0.06203119294637216</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0463821892393321</v>
+        <v>0.04649000464900046</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.68485346197715</v>
+        <v>44.81247717854886</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.61441126247374</v>
+        <v>76.65269837744525</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.07658909232063</v>
+        <v>22.08994582585784</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22390.58658977705</v>
+        <v>22411.12809257272</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02396053303899071</v>
+        <v>0.02696168414029931</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44401154119674</v>
+        <v>24.44689948358316</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24791.68112093274</v>
+        <v>24802.35126477752</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1337667690722051</v>
+        <v>0.1365364706454284</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4842,6 +4842,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>21822.75</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.0620311929464</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4882,7 +4915,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21822.75</v>
+        <v>22090</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.51</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.1194029850746269</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1014.539748953975</v>
+        <v>1015.16544117647</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06203119294637216</v>
+        <v>0.06289322553935284</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04649000464900046</v>
+        <v>0.04595588235294117</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>88.05970149253731</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>44.81247717854886</v>
+        <v>45.15729021574113</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>76.65269837744525</v>
+        <v>75.18897810949845</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.08994582585784</v>
+        <v>22.12603297315027</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22411.12809257272</v>
+        <v>22461.58402467323</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02696168414029931</v>
+        <v>0.01682136825139113</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.44689948358316</v>
+        <v>24.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24802.35126477752</v>
+        <v>24820.7950367647</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1365364706454284</v>
+        <v>0.1236213235294117</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4875,6 +4875,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>22090</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.119402985075</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.06289322553939999</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4915,7 +4948,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22090</v>
+        <v>22038</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.76</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1194029850746269</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1015.16544117647</v>
+        <v>1015.576036866359</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06289322553935284</v>
+        <v>0.06314601697056998</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04595588235294117</v>
+        <v>0.04608294930875576</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.05970149253731</v>
+        <v>88.80597014925374</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>45.15729021574113</v>
+        <v>45.25840678822799</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.18897810949845</v>
+        <v>75.74170114094601</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.12603297315027</v>
+        <v>22.13661554472226</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22461.58402467323</v>
+        <v>22481.41628454328</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01682136825139113</v>
+        <v>0.02012053201485053</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24820.7950367647</v>
+        <v>24830.83410138249</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1236213235294117</v>
+        <v>0.1267281105990783</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4908,6 +4908,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>22038</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.111940298507</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.0631460169706</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4948,7 +4981,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22038</v>
+        <v>22180.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.7</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1119402985074627</v>
+        <v>0.1716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1015.576036866359</v>
+        <v>1016.069628950985</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06314601697056998</v>
+        <v>0.06399504292488722</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04608294930875576</v>
+        <v>0.04580852038479157</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>88.80597014925374</v>
+        <v>82.83582089552239</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>45.25840678822799</v>
+        <v>45.59801716995489</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.74170114094601</v>
+        <v>71.66447977785214</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.13661554472226</v>
+        <v>22.17215819695842</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22481.41628454328</v>
+        <v>22528.45655222609</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.02012053201485053</v>
+        <v>0.01567376074019355</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24830.83410138249</v>
+        <v>24842.90242785158</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1267281105990783</v>
+        <v>0.1200183234081538</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4941,6 +4941,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>22180.8</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.171641791045</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.06399504292490001</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4981,7 +5014,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22180.8</v>
+        <v>22270.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.83</v>
+        <v>21.89</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1716417910447761</v>
+        <v>0.1865671641791045</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1016.069628950985</v>
+        <v>1017.361809045226</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06399504292488722</v>
+        <v>0.06728048615240279</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04580852038479157</v>
+        <v>0.04568296025582458</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>82.83582089552239</v>
+        <v>81.34328358208955</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>45.59801716995489</v>
+        <v>46.91219446096111</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.66447977785214</v>
+        <v>71.01395684575101</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.17215819695842</v>
+        <v>22.22077797161545</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22528.45655222609</v>
+        <v>22606.570875595</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01567376074019355</v>
+        <v>0.01511091693081079</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24842.90242785158</v>
+        <v>24874.49623115578</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1200183234081538</v>
+        <v>0.1169483782549108</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4974,6 +4974,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>22270.05</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.186567164179</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.0672804861524</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5014,7 +5047,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22270.05</v>
+        <v>22041.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.89</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1865671641791045</v>
+        <v>0.09701492537313433</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1017.361809045226</v>
+        <v>1025.190697674419</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06728048615240279</v>
+        <v>0.07436699021691928</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04568296025582458</v>
+        <v>0.04651162790697674</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>81.34328358208955</v>
+        <v>90.29850746268657</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>46.91219446096111</v>
+        <v>49.74679608676771</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>71.01395684575101</v>
+        <v>78.13299404991091</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.22077797161545</v>
+        <v>22.26424732148</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22606.570875595</v>
+        <v>22825.09924470389</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.01511091693081079</v>
+        <v>0.03554638704558144</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45</v>
+        <v>24.46070852679343</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>24874.49623115578</v>
+        <v>25076.89084019395</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1169483782549108</v>
+        <v>0.1377073733392291</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5007,6 +5007,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>22041.6</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0970149253731</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.07436699021690001</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5047,7 +5080,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>22041.6</v>
+        <v>21837.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.09701492537313433</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1025.190697674419</v>
+        <v>1025.253521126761</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07436699021691928</v>
+        <v>0.06973445186422089</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04651162790697674</v>
+        <v>0.04694835680751173</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>90.29850746268657</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.74679608676771</v>
+        <v>47.89378074568835</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.13299404991091</v>
+        <v>78.62186556699008</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.26424732148</v>
+        <v>22.23188391929408</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22825.09924470389</v>
+        <v>22793.31726953766</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.03554638704558144</v>
+        <v>0.04375041874620078</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.46070852679343</v>
+        <v>24.45</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25076.89084019395</v>
+        <v>25067.4485915493</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1377073733392291</v>
+        <v>0.147887323943662</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5040,6 +5040,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>21837.9</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.06973445186420001</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5080,7 +5113,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21837.9</v>
+        <v>21696.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.3</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1025.253521126761</v>
+        <v>1027.785409758408</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.06973445186422089</v>
+        <v>0.07237618724161354</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04694835680751173</v>
+        <v>0.0473709142586452</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>47.89378074568835</v>
+        <v>48.95047489664542</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>78.62186556699008</v>
+        <v>82.07320217048616</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.23188391929408</v>
+        <v>22.24383965883062</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22793.31726953766</v>
+        <v>22861.89385835156</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04375041874620078</v>
+        <v>0.05371102126151683</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45</v>
+        <v>24.45395117269439</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25067.4485915493</v>
+        <v>25133.41422623981</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.147887323943662</v>
+        <v>0.1584060242868019</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5073,6 +5073,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>21696.55</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.0723761872416</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5113,7 +5146,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,8 +568,8 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21696.55</v>
+        <v>21427.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.11</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1027.785409758408</v>
+        <v>1028.195777351247</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07237618724161354</v>
+        <v>0.07252056805946783</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0473709142586452</v>
+        <v>0.04798464491362764</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>48.95047489664542</v>
+        <v>49.00822722378713</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.07320217048616</v>
+        <v>83.13530398803167</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.24383965883062</v>
+        <v>22.24449308516056</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22861.89385835156</v>
+        <v>22871.69385948111</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05371102126151683</v>
+        <v>0.067394101975075</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45395117269439</v>
+        <v>24.45444124244185</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25133.41422623981</v>
+        <v>25143.95322296291</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1584060242868019</v>
+        <v>0.1734376795797434</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5106,6 +5106,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>21427.6</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.0725205680595</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5146,7 +5179,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21427.6</v>
+        <v>21608.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>20.84</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1028.195777351247</v>
+        <v>1029.478323010958</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07252056805946783</v>
+        <v>0.07395782263392658</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04798464491362764</v>
+        <v>0.04764173415912339</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.00822722378713</v>
+        <v>49.58312905357063</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.13530398803167</v>
+        <v>83.3077745369667</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.24449308516056</v>
+        <v>22.254988443602</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22871.69385948111</v>
+        <v>22911.02818154762</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.067394101975075</v>
+        <v>0.06026624314444939</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45444124244185</v>
+        <v>24.45931969511173</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25143.95322296291</v>
+        <v>25180.33942171251</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1734376795797434</v>
+        <v>0.1652844066275241</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5139,6 +5139,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>21608.75</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.07395782263389999</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5179,7 +5212,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -568,7 +568,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21608.75</v>
+        <v>21734.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>20.99</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1029.478323010958</v>
+        <v>1037.960840496657</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.07395782263392658</v>
+        <v>0.08320011876887312</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04764173415912339</v>
+        <v>0.04775549188156638</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>49.58312905357063</v>
+        <v>53.28004750754925</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.3077745369667</v>
+        <v>84.41685007316029</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.254988443602</v>
+        <v>22.4577706210206</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>22911.02818154762</v>
+        <v>23310.28646947568</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06026624314444939</v>
+        <v>0.07248188257022936</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>24.45931969511173</v>
+        <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25180.33942171251</v>
+        <v>25409.28137535816</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1652844066275241</v>
+        <v>0.1690544412607449</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5172,6 +5172,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>21734.9</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.0832001187689</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5212,7 +5245,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9702,12 +9735,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>ICICI Life Insurance Ltd.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICILIFE</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9722,12 +9755,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ICICI Prudential Asset Management Company Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>ICICIAMC</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -9742,12 +9775,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
+          <t>ICICI Prudential Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>ICICIAMC</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21734.9</v>
+        <v>21727.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>20.94</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1037.960840496657</v>
+        <v>1039.093735054998</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08320011876887312</v>
+        <v>0.08043703341144659</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04775549188156638</v>
+        <v>0.04782400765184122</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>53.28004750754925</v>
+        <v>52.17481336457863</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>84.41685007316029</v>
+        <v>84.08527983026912</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.4577706210206</v>
+        <v>22.40160372748188</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23310.28646947568</v>
+        <v>23277.3660884111</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07248188257022936</v>
+        <v>0.07133446807660793</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25409.28137535816</v>
+        <v>25437.01463414634</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1690544412607449</v>
+        <v>0.1707317073170733</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5205,6 +5205,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>21727.45</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.0804370334114</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5245,7 +5278,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -569,7 +569,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21727.45</v>
+        <v>21941.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>20.91</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02238805970149254</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1039.093735054998</v>
+        <v>1039.388915206064</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08043703341144659</v>
+        <v>0.08094294842199701</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04782400765184122</v>
+        <v>0.0473709142586452</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.76119402985076</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.17481336457863</v>
+        <v>52.3771793687988</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>84.08527983026912</v>
+        <v>83.10121351213218</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.40160372748188</v>
+        <v>22.4130518614349</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23277.3660884111</v>
+        <v>23295.87766071406</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07133446807660793</v>
+        <v>0.06172675800260086</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25437.01463414634</v>
+        <v>25444.24064424444</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1707317073170733</v>
+        <v>0.1596399810516345</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5238,6 +5238,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>21941.5</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.08094294842200001</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5278,7 +5311,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-500.xlsx
+++ b/docs/downloads/indices/nifty-500.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>21941.5</v>
+        <v>21895.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>21.11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.02238805970149254</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1039.388915206064</v>
+        <v>1042.661904761905</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.08094294842199701</v>
+        <v>0.08415181299038332</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0473709142586452</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>97.76119402985076</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>52.3771793687988</v>
+        <v>53.66072519615333</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>83.10121351213218</v>
+        <v>84.53105337974152</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>22.4130518614349</v>
+        <v>22.46961513538889</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>23295.87766071406</v>
+        <v>23428.2117163315</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06172675800260086</v>
+        <v>0.06998167311375636</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>24.48</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>25444.24064424444</v>
+        <v>25524.36342857143</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.1596399810516345</v>
+        <v>0.1657142857142859</v>
       </c>
     </row>
     <row r="16">
@@ -4289,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5271,6 +5271,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>21895.9</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0223880597015</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.0841518129904</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5311,7 +5344,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
